--- a/pacjenci/DOROTA PIETRAS.xlsx
+++ b/pacjenci/DOROTA PIETRAS.xlsx
@@ -483,7 +483,11 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -523,7 +527,11 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -563,7 +571,11 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Do oceny</t>

--- a/pacjenci/DOROTA PIETRAS.xlsx
+++ b/pacjenci/DOROTA PIETRAS.xlsx
@@ -413,191 +413,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>21.11.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak obwodowy i skórny z komórek T. Ocena zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 108mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne przedziału 2 obustronnie wielkości do 11mm.  Dość liczne, drobne zwapnienia w tkance podskórnej głowy, zwłaszcza w okolicy potylicznej i ciemieniowej. Aplazja lewej zatoki czołowej, hypoplazja prawej. Ok. 14mm zmiana miękkotkankowa z wydatnym zwapnieniem w prawej zatoce szczękowej - do kontroli laryngologicznej. Ok. 13mm polipowate zgrubienie błony śluzowej oraz niepełna przegroda kostna w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne pachowe lewe wielkości do 15x10mm, SUV max do 6,9. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany guzkowo-włókniste w szczycie płuca lewego. Drobne zmiany włókniste w szczycie pluca prawego. Drobne obwodowe zmiany włókniste w segm. 6 obu płuc. Pasmowate zmiany włókniste w segm. 8 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona dodatkowa o średnicy 23mm. Zwraca uwagę znaczna ilość gazu w pętlach jelita cienkiego. W grzbietowo-lewobocznej części miednicy w ścisłym przyleganiu do grzbietowo-lewobocznego obrysu trzonu macicy widoczna jest miękkotkankowa zmiana wielkości ok. 39mm - mięśniak? inne - do oceny w badaniu TK/MR z kontrastem dożylnym. Poza tym niejednorodne cieniowanie w przeglądowym badaniu TK powiększonego trzonu macicy - do oceny j.w. Węzły chłonne pachwinowe wielkości do 11mm.   Układ kostny: Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z odcinkowym pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Drobna spondylolisteza przednia na poziomie L4/L5. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych, wydatne w odcinku lędźwiowym kręgosłupa. Ok. 5mm wyspa kostna w lewej kości kulszowej. Obwodowe torbielki oraz drobne zwapnienia w głowach obu kości udowych.  Inne: Pobudzenie metaboliczne w topografii blizny w obrębie powłok brzucha, SUV max do 3,3 - procesy gojenia.    Wartości referencyjne: MBPS SUVmax do 1,9; Prawy płat wątroby SUVmax do 2,7.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych pachowych lewych. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>6.9</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>31.01.2023</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak z komórek T, typ jelitowy (MEITL). Stan po odcinkowej resekcji jelita cienkiego (27.09.2022r). Stan po chemioterapii (3 cykle). Ocena chemiowrażliwości przed mobilizacją komórek krwiotwórczych.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 89mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne przedziału 2 obustronnie wielkości do 11mm.  Dość liczne, drobne zwapnienia w tkance podskórnej głowy, zwłaszcza w okolicy potylicznej i ciemieniowej. Aplazja lewej zatoki czołowej, hipoplazja prawej. Ok. 14mm zmiana miękkotkankowa z wydatnym zwapnieniem w prawej zatoce szczękowej - do kontroli laryngologicznej. Ok. 13mm polipowate zgrubienie błony śluzowej oraz niepełna przegroda kostna w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne pachowe lewe wielkości do 12x7mm, SUV max do 1,4  [Im fuz 91]. Drobne zmiany guzkowo-włókniste w szczycie płuca lewego. Drobne zmiany włókniste w szczycie płuca prawego. Drobne obwodowe zmiany włókniste w segm. 6 obu płuc. Pasmowate zmiany włókniste w segm. 8 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Stan po założeniu portu naczyniowego po stronie prawej.  Brzuch i miednica: Aktywna metabolicznie owalna zmiana miękkotkanowa w topografii zstępnicy (dół biodrowy lewy) wlk. 33x29mm, SUVmax 8,9  [Im fuz 200]. Odcinkowy rozlany aktywny metabolizm FDG w obrębie jelita w okolicy guza, SUVmax  do 6,2. Aktywna metabolicznie zmiana w obrębie esicy (na prawo i do tyłu od macicy) wlk. 30x24mm, SUVmax 8,3   [Im fuz 230] - w pierwszej kolejności naciek chłoniakowy. Aktywny metabolicznie obszar średnicy 16mm wg PET w topografii przydatków prawych, SUVmax 5,7  [Im fuz 229]  - do kontroli. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona dodatkowa o średnicy 23mm. Węzły chłonne pachwinowe wielkości do 11mm.   Układ kostny: Rozlane pobudzenie metaboliczne w układzie kostnym - w pierwszej kolejności związane z zastosowanym leczeniem. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Drobna spondylolisteza przednia na poziomie L4/L5. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych, wydatne w odcinku lędźwiowym kręgosłupa. Ok. 5mm wyspa kostna w lewej kości kulszowej. Obwodowe torbielki oraz drobne zwapnienia w głowach obu kości udowych.  Inne: Pobudzenie metaboliczne w topografii blizny w obrębie powłok brzucha, SUV max do 3,3 - procesy gojenia.    Wartości referencyjne: MBPS SUVmax do 1,7 Prawy płat wątroby SUVmax do 2,4.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie zmian miękkotkankowych w obrębie zstępnicy i esicy - w pierwszej kolejności proces chłoniakowy - zmiany nie były obecne w poprzednim badaniu PET z dnia 21.11.2022r. Aktualnie węzły chłonnych pachowe są nieaktywne. Poza tym w badaniu widoczny jest aktywny metabolicznie obszar średnicy 16mm wg PET w topografii przydatków prawych - do kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>8.9</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>08.05.2023</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak z komórek T, typ jelitowy (MEITL). Stan po odcinkowej resekcji jelita cienkiego (27.09.2022r). Stan po chemioterapii. Stan po mobilizacją komórek krwiotwórczych. Ocena odpowiedzi przed auto PBSCT.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 93mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dość liczne, drobne zwapnienia w tkance podskórnej głowy, zwłaszcza w okolicy potylicznej i ciemieniowej. Aplazja lewej zatoki czołowej, hipoplazja prawej. Ok. 14mm zmiana miękkotkankowa z wydatnym zwapnieniem w prawej zatoce szczękowej - do kontroli laryngologicznej. Ok. 13mm polipowate zgrubienie błony śluzowej oraz niepełna przegroda kostna w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe lewe wielkości do 11mm. Drobne zmiany guzkowo-włókniste w szczycie płuca lewego. Drobne zmiany włókniste w szczycie płuca prawego. Drobne obwodowe zmiany włókniste w segm. 6 obu płuc. Pasmowate zmiany włókniste w segm. 8 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Stan po założeniu portu naczyniowego po stronie prawej.  Brzuch i miednica: Pobudzona metabolicznie owalna zmiana miękkotkankowa w łączności ze ścianą  zstępnicy (dół biodrowy lewy) wielkości 35x23mm, SUVmax 3,6. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona dodatkowa o średnicy 25mm. Węzły chłonne pachwinowe wielkości do 11mm. Macica z uwypuklającym się ku tyłowi mięśniakiem wielkości 40mm.   Układ kostny: Rozlane pobudzenie metaboliczne w układzie kostnym - w pierwszej kolejności związane z zastosowanym leczeniem. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Drobna spondylolisteza przednia na poziomie L4/L5. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych, wydatne w odcinku lędźwiowym kręgosłupa. Ok. 5mm wyspa kostna w lewej kości kulszowej. Obwodowe torbielki oraz drobne zwapnienia w głowach obu kości udowych.  Wartości referencyjne: MBPS SUVmax do 1,8 Prawy płat wątroby SUVmax do 3,2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono pobudzoną metabolicznie owalną zmianę miękkotkankową w topografii zstępnicy. Poza tym uwidoczniono bardzo dobrą odpowiedź metaboliczną na stosowane leczenie. Ponadto jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>3.6</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/DOROTA PIETRAS.xlsx
+++ b/pacjenci/DOROTA PIETRAS.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 108mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne przedziału 2 obustronnie wielkości do 11mm.  Dość liczne, drobne zwapnienia w tkance podskórnej głowy, zwłaszcza w okolicy potylicznej i ciemieniowej. Aplazja lewej zatoki czołowej, hypoplazja prawej. Ok. 14mm zmiana miękkotkankowa z wydatnym zwapnieniem w prawej zatoce szczękowej - do kontroli laryngologicznej. Ok. 13mm polipowate zgrubienie błony śluzowej oraz niepełna przegroda kostna w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne pachowe lewe wielkości do 15x10mm, SUV max do 6,9. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany guzkowo-włókniste w szczycie płuca lewego. Drobne zmiany włókniste w szczycie pluca prawego. Drobne obwodowe zmiany włókniste w segm. 6 obu płuc. Pasmowate zmiany włókniste w segm. 8 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona dodatkowa o średnicy 23mm. Zwraca uwagę znaczna ilość gazu w pętlach jelita cienkiego. W grzbietowo-lewobocznej części miednicy w ścisłym przyleganiu do grzbietowo-lewobocznego obrysu trzonu macicy widoczna jest miękkotkankowa zmiana wielkości ok. 39mm - mięśniak? inne - do oceny w badaniu TK/MR z kontrastem dożylnym. Poza tym niejednorodne cieniowanie w przeglądowym badaniu TK powiększonego trzonu macicy - do oceny j.w. Węzły chłonne pachwinowe wielkości do 11mm.   Układ kostny: Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z odcinkowym pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Drobna spondylolisteza przednia na poziomie L4/L5. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych, wydatne w odcinku lędźwiowym kręgosłupa. Ok. 5mm wyspa kostna w lewej kości kulszowej. Obwodowe torbielki oraz drobne zwapnienia w głowach obu kości udowych.  Inne: Pobudzenie metaboliczne w topografii blizny w obrębie powłok brzucha, SUV max do 3,3 - procesy gojenia.    Wartości referencyjne: MBPS SUVmax do 1,9; Prawy płat wątroby SUVmax do 2,7.</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne przedziału 2 obustronnie wielkości do 11mm.  Dość liczne, drobne zwapnienia w tkance podskórnej głowy, zwłaszcza w okolicy potylicznej i ciemieniowej. Aplazja lewej zatoki czołowej, hypoplazja prawej. Ok. 14mm zmiana miękkotkankowa z wydatnym zwapnieniem w prawej zatoce szczękowej - do kontroli laryngologicznej. Ok. 13mm polipowate zgrubienie błony śluzowej oraz niepełna przegroda kostna w lewej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne pachowe lewe wielkości do 15x10mm, SUV max do 6,9. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany guzkowo-włókniste w szczycie płuca lewego. Drobne zmiany włókniste w szczycie pluca prawego. Drobne obwodowe zmiany włókniste w segm. 6 obu płuc. Pasmowate zmiany włókniste w segm. 8 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona dodatkowa o średnicy 23mm. Zwraca uwagę znaczna ilość gazu w pętlach jelita cienkiego. W grzbietowo-lewobocznej części miednicy w ścisłym przyleganiu do grzbietowo-lewobocznego obrysu trzonu macicy widoczna jest miękkotkankowa zmiana wielkości ok. 39mm - mięśniak? inne - do oceny w badaniu TK/MR z kontrastem dożylnym. Poza tym niejednorodne cieniowanie w przeglądowym badaniu TK powiększonego trzonu macicy - do oceny j.w. Węzły chłonne pachwinowe wielkości do 11mm.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z odcinkowym pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Drobna spondylolisteza przednia na poziomie L4/L5. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych, wydatne w odcinku lędźwiowym kręgosłupa. Ok. 5mm wyspa kostna w lewej kości kulszowej. Obwodowe torbielki oraz drobne zwapnienia w głowach obu kości udowych.  Inne: Pobudzenie metaboliczne w topografii blizny w obrębie powłok brzucha, SUV max do 3,3 - procesy gojenia.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie węzłów chłonnych pachowych lewych. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>6.9</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 89mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne przedziału 2 obustronnie wielkości do 11mm.  Dość liczne, drobne zwapnienia w tkance podskórnej głowy, zwłaszcza w okolicy potylicznej i ciemieniowej. Aplazja lewej zatoki czołowej, hipoplazja prawej. Ok. 14mm zmiana miękkotkankowa z wydatnym zwapnieniem w prawej zatoce szczękowej - do kontroli laryngologicznej. Ok. 13mm polipowate zgrubienie błony śluzowej oraz niepełna przegroda kostna w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne pachowe lewe wielkości do 12x7mm, SUV max do 1,4  [Im fuz 91]. Drobne zmiany guzkowo-włókniste w szczycie płuca lewego. Drobne zmiany włókniste w szczycie płuca prawego. Drobne obwodowe zmiany włókniste w segm. 6 obu płuc. Pasmowate zmiany włókniste w segm. 8 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Stan po założeniu portu naczyniowego po stronie prawej.  Brzuch i miednica: Aktywna metabolicznie owalna zmiana miękkotkanowa w topografii zstępnicy (dół biodrowy lewy) wlk. 33x29mm, SUVmax 8,9  [Im fuz 200]. Odcinkowy rozlany aktywny metabolizm FDG w obrębie jelita w okolicy guza, SUVmax  do 6,2. Aktywna metabolicznie zmiana w obrębie esicy (na prawo i do tyłu od macicy) wlk. 30x24mm, SUVmax 8,3   [Im fuz 230] - w pierwszej kolejności naciek chłoniakowy. Aktywny metabolicznie obszar średnicy 16mm wg PET w topografii przydatków prawych, SUVmax 5,7  [Im fuz 229]  - do kontroli. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona dodatkowa o średnicy 23mm. Węzły chłonne pachwinowe wielkości do 11mm.   Układ kostny: Rozlane pobudzenie metaboliczne w układzie kostnym - w pierwszej kolejności związane z zastosowanym leczeniem. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Drobna spondylolisteza przednia na poziomie L4/L5. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych, wydatne w odcinku lędźwiowym kręgosłupa. Ok. 5mm wyspa kostna w lewej kości kulszowej. Obwodowe torbielki oraz drobne zwapnienia w głowach obu kości udowych.  Inne: Pobudzenie metaboliczne w topografii blizny w obrębie powłok brzucha, SUV max do 3,3 - procesy gojenia.    Wartości referencyjne: MBPS SUVmax do 1,7 Prawy płat wątroby SUVmax do 2,4.</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne przedziału 2 obustronnie wielkości do 11mm.  Dość liczne, drobne zwapnienia w tkance podskórnej głowy, zwłaszcza w okolicy potylicznej i ciemieniowej. Aplazja lewej zatoki czołowej, hipoplazja prawej. Ok. 14mm zmiana miękkotkankowa z wydatnym zwapnieniem w prawej zatoce szczękowej - do kontroli laryngologicznej. Ok. 13mm polipowate zgrubienie błony śluzowej oraz niepełna przegroda kostna w lewej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne pachowe lewe wielkości do 12x7mm, SUV max do 1,4  [Im fuz 91]. Drobne zmiany guzkowo-włókniste w szczycie płuca lewego. Drobne zmiany włókniste w szczycie płuca prawego. Drobne obwodowe zmiany włókniste w segm. 6 obu płuc. Pasmowate zmiany włókniste w segm. 8 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Stan po założeniu portu naczyniowego po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Aktywna metabolicznie owalna zmiana miękkotkanowa w topografii zstępnicy (dół biodrowy lewy) wlk. 33x29mm, SUVmax 8,9  [Im fuz 200]. Odcinkowy rozlany aktywny metabolizm FDG w obrębie jelita w okolicy guza, SUVmax  do 6,2. Aktywna metabolicznie zmiana w obrębie esicy (na prawo i do tyłu od macicy) wlk. 30x24mm, SUVmax 8,3   [Im fuz 230] - w pierwszej kolejności naciek chłoniakowy. Aktywny metabolicznie obszar średnicy 16mm wg PET w topografii przydatków prawych, SUVmax 5,7  [Im fuz 229]  - do kontroli. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona dodatkowa o średnicy 23mm. Węzły chłonne pachwinowe wielkości do 11mm.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Rozlane pobudzenie metaboliczne w układzie kostnym - w pierwszej kolejności związane z zastosowanym leczeniem. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Drobna spondylolisteza przednia na poziomie L4/L5. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych, wydatne w odcinku lędźwiowym kręgosłupa. Ok. 5mm wyspa kostna w lewej kości kulszowej. Obwodowe torbielki oraz drobne zwapnienia w głowach obu kości udowych.  Inne: Pobudzenie metaboliczne w topografii blizny w obrębie powłok brzucha, SUV max do 3,3 - procesy gojenia.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie zmian miękkotkankowych w obrębie zstępnicy i esicy - w pierwszej kolejności proces chłoniakowy - zmiany nie były obecne w poprzednim badaniu PET z dnia 21.11.2022r. Aktualnie węzły chłonnych pachowe są nieaktywne. Poza tym w badaniu widoczny jest aktywny metabolicznie obszar średnicy 16mm wg PET w topografii przydatków prawych - do kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>8.9</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 93mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dość liczne, drobne zwapnienia w tkance podskórnej głowy, zwłaszcza w okolicy potylicznej i ciemieniowej. Aplazja lewej zatoki czołowej, hipoplazja prawej. Ok. 14mm zmiana miękkotkankowa z wydatnym zwapnieniem w prawej zatoce szczękowej - do kontroli laryngologicznej. Ok. 13mm polipowate zgrubienie błony śluzowej oraz niepełna przegroda kostna w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe lewe wielkości do 11mm. Drobne zmiany guzkowo-włókniste w szczycie płuca lewego. Drobne zmiany włókniste w szczycie płuca prawego. Drobne obwodowe zmiany włókniste w segm. 6 obu płuc. Pasmowate zmiany włókniste w segm. 8 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Stan po założeniu portu naczyniowego po stronie prawej.  Brzuch i miednica: Pobudzona metabolicznie owalna zmiana miękkotkankowa w łączności ze ścianą  zstępnicy (dół biodrowy lewy) wielkości 35x23mm, SUVmax 3,6. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona dodatkowa o średnicy 25mm. Węzły chłonne pachwinowe wielkości do 11mm. Macica z uwypuklającym się ku tyłowi mięśniakiem wielkości 40mm.   Układ kostny: Rozlane pobudzenie metaboliczne w układzie kostnym - w pierwszej kolejności związane z zastosowanym leczeniem. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Drobna spondylolisteza przednia na poziomie L4/L5. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych, wydatne w odcinku lędźwiowym kręgosłupa. Ok. 5mm wyspa kostna w lewej kości kulszowej. Obwodowe torbielki oraz drobne zwapnienia w głowach obu kości udowych.  Wartości referencyjne: MBPS SUVmax do 1,8 Prawy płat wątroby SUVmax do 3,2</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Dość liczne, drobne zwapnienia w tkance podskórnej głowy, zwłaszcza w okolicy potylicznej i ciemieniowej. Aplazja lewej zatoki czołowej, hipoplazja prawej. Ok. 14mm zmiana miękkotkankowa z wydatnym zwapnieniem w prawej zatoce szczękowej - do kontroli laryngologicznej. Ok. 13mm polipowate zgrubienie błony śluzowej oraz niepełna przegroda kostna w lewej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe lewe wielkości do 11mm. Drobne zmiany guzkowo-włókniste w szczycie płuca lewego. Drobne zmiany włókniste w szczycie płuca prawego. Drobne obwodowe zmiany włókniste w segm. 6 obu płuc. Pasmowate zmiany włókniste w segm. 8 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Stan po założeniu portu naczyniowego po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pobudzona metabolicznie owalna zmiana miękkotkankowa w łączności ze ścianą  zstępnicy (dół biodrowy lewy) wielkości 35x23mm, SUVmax 3,6. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona dodatkowa o średnicy 25mm. Węzły chłonne pachwinowe wielkości do 11mm. Macica z uwypuklającym się ku tyłowi mięśniakiem wielkości 40mm.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Rozlane pobudzenie metaboliczne w układzie kostnym - w pierwszej kolejności związane z zastosowanym leczeniem. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Drobna spondylolisteza przednia na poziomie L4/L5. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych, wydatne w odcinku lędźwiowym kręgosłupa. Ok. 5mm wyspa kostna w lewej kości kulszowej. Obwodowe torbielki oraz drobne zwapnienia w głowach obu kości udowych.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono pobudzoną metabolicznie owalną zmianę miękkotkankową w topografii zstępnicy. Poza tym uwidoczniono bardzo dobrą odpowiedź metaboliczną na stosowane leczenie. Ponadto jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>3.6</v>
       </c>
     </row>
